--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122461803</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57398</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Oxhagsviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566927</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6323125</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Långemåla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Hedin, Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122442542</v>
       </c>
       <c r="B2" t="n">
-        <v>39820</v>
+        <v>39825</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>101166</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mindre träfjäril</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Acossus terebra</t>
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -819,11 +809,6 @@
       </c>
       <c r="E3" t="n">
         <v>102977</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122442542</v>
       </c>
       <c r="B2" t="n">
-        <v>39825</v>
+        <v>39829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>101166</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mindre träfjäril</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Acossus terebra</t>
@@ -766,6 +771,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -795,7 +805,7 @@
         <v>122461803</v>
       </c>
       <c r="B3" t="n">
-        <v>57398</v>
+        <v>57402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,6 +819,11 @@
       </c>
       <c r="E3" t="n">
         <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122442542</v>
       </c>
       <c r="B2" t="n">
-        <v>39829</v>
+        <v>39830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>122461803</v>
       </c>
       <c r="B3" t="n">
-        <v>57402</v>
+        <v>57403</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,234 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122836079</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oxhagsviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566927</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6323125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Långemåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122836077</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58183</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxhagsviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566927</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6323125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Långemåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122836079</v>
+        <v>122836077</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>58183</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,33 +932,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122836077</v>
+        <v>122836079</v>
       </c>
       <c r="B5" t="n">
-        <v>58183</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,33 +1046,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122836077</v>
+        <v>122836079</v>
       </c>
       <c r="B4" t="n">
-        <v>58183</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,33 +932,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122836079</v>
+        <v>122836077</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>58183</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,33 +1046,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122836077</v>
+        <v>122836079</v>
       </c>
       <c r="B4" t="n">
-        <v>58183</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,33 +932,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122836079</v>
+        <v>122836077</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>58186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,33 +1046,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122836079</v>
+        <v>122836077</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>58186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,33 +932,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122836077</v>
+        <v>122836079</v>
       </c>
       <c r="B5" t="n">
-        <v>58186</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,33 +1046,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122442542</v>
       </c>
       <c r="B2" t="n">
-        <v>39923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,12 +800,7 @@
         <v>122461803</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122836077</v>
+        <v>122836079</v>
       </c>
       <c r="B4" t="n">
-        <v>58186</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,33 +917,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1030,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122836079</v>
+        <v>122836077</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,33 +1026,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 57171-2022 artfynd.xlsx
+++ b/artfynd/A 57171-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122442542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122461803</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122836079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,8 +1141,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122836077</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>